--- a/notebooks/01_first_analysis/totales_checkers.xlsx
+++ b/notebooks/01_first_analysis/totales_checkers.xlsx
@@ -413,18 +413,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" t="inlineStr">
         <is>
-          <t>Items Cumplidos</t>
+          <t>Items Fulfilled</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Cumplimiento</t>
+          <t>Compliance</t>
         </is>
       </c>
     </row>
@@ -444,8 +444,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AdaptaTuTexto (deepseek-v3.2)
-Sencillo B2</t>
+          <t>Asistente Lectura Facilitada "Francisco Javier Alvarez Jimenez"</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -471,20 +470,20 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SimpleText (ClearText)</t>
+          <t>FACILE</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="C5" t="n">
-        <v>96.667</v>
+        <v>93.333</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FACILE</t>
+          <t>Modelo_Qwen3.5_9B</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -497,188 +496,91 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GPT 5.4 Think</t>
+          <t>Placea</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="C7" t="n">
-        <v>93.333</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AdaptaTuTexto (deepseek-v3.2)
-Facil B1</t>
+          <t xml:space="preserve">Asistente de lectura fácil “Mark Jonathan Camacho Escatel”: </t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="C8" t="n">
-        <v>93.333</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>deepseek-v3.2</t>
+          <t>GPT 5.4 Think</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="C9" t="n">
-        <v>93.333</v>
+        <v>83.333</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Claude Sonnet 4.6</t>
+          <t>SimpleText (ClearText)</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="C10" t="n">
-        <v>93.333</v>
+        <v>83.333</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Placea</t>
+          <t>deepseek-v3.2</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="C11" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asistente de lectura fácil “Mark Jonathan Camacho Escatel”: </t>
+          <t>Gemini 3.1 Pro</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="C12" t="n">
-        <v>90</v>
+        <v>76.667</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Asistente Lectura Facilitada "Francisco Javier Alvarez Jimenez"</t>
+          <t>Claude Sonnet 4.6</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Gemini 3.1 Pro</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>13</v>
-      </c>
-      <c r="C14" t="n">
-        <v>86.667</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>AdaptaTuTexto (Gemini 3.1 Pro)
-Facil B1</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="C15" t="n">
-        <v>83.333</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>AdaptaTuTexto (deepseek-v3.2)
-Muy A2</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="C16" t="n">
-        <v>83.333</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>AdaptaTuTexto (Gemini 3.1 Pro)
-Sencillo B2.1</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>12</v>
-      </c>
-      <c r="C17" t="n">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Modelo_Qwen3.5_9B</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>12</v>
-      </c>
-      <c r="C18" t="n">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>AdaptaTuTexto (Gemini 3.1 Pro)
-Muy A2</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="C19" t="n">
-        <v>76.667</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>AdaptaTuTexto (Gemini 3.1 Pro)
-Sencillo B2</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>11</v>
-      </c>
-      <c r="C20" t="n">
         <v>73.333</v>
       </c>
     </row>

--- a/notebooks/01_first_analysis/totales_checkers.xlsx
+++ b/notebooks/01_first_analysis/totales_checkers.xlsx
@@ -444,14 +444,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Asistente Lectura Facilitada "Francisco Javier Alvarez Jimenez"</t>
+          <t>FACILE</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C3" t="n">
-        <v>100</v>
+        <v>93.333</v>
       </c>
     </row>
     <row r="4">
@@ -461,16 +461,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="C4" t="n">
-        <v>96.667</v>
+        <v>93.333</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FACILE</t>
+          <t>Claude Sonnet 4.6</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -483,7 +483,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Modelo_Qwen3.5_9B</t>
+          <t>SimpleText (ClearText)</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -496,59 +496,59 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Placea</t>
+          <t>GPT 5.4 Think</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="C7" t="n">
-        <v>90</v>
+        <v>93.333</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asistente de lectura fácil “Mark Jonathan Camacho Escatel”: </t>
+          <t>deepseek-v3.2</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="C8" t="n">
-        <v>90</v>
+        <v>93.333</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GPT 5.4 Think</t>
+          <t>Asistente Lectura Facilitada "Francisco Javier Alvarez Jimenez"</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="C9" t="n">
-        <v>83.333</v>
+        <v>86.667</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SimpleText (ClearText)</t>
+          <t>Placea</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="C10" t="n">
-        <v>83.333</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>deepseek-v3.2</t>
+          <t>Gemini 3.1 Pro</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -561,27 +561,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Gemini 3.1 Pro</t>
+          <t xml:space="preserve">Asistente de lectura fácil “Mark Jonathan Camacho Escatel”: </t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="C12" t="n">
-        <v>76.667</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Claude Sonnet 4.6</t>
+          <t>Modelo_Qwen3.5_9B</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>73.333</v>
+        <v>66.667</v>
       </c>
     </row>
   </sheetData>
